--- a/output/pdf_financials_xlsx/UFC.xlsx
+++ b/output/pdf_financials_xlsx/UFC.xlsx
@@ -879,25 +879,25 @@
         <v>0.099415</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.117744</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.145402</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.102374</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.102374</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.456227</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.450974</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.331287</v>
       </c>
     </row>
     <row r="13">
@@ -1529,25 +1529,25 @@
         <v>10.745342</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>5.462709</v>
+        <v>5.344965</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>6.759202</v>
+        <v>6.6138</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>9.692503</v>
+        <v>9.590128999999999</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>9.692503</v>
+        <v>9.590128999999999</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>7.963575</v>
+        <v>7.507348</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>12.436601</v>
+        <v>11.985627</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>6.373205</v>
+        <v>6.041918</v>
       </c>
     </row>
     <row r="28">
@@ -1609,25 +1609,25 @@
         <v>10.745342</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>5.462709</v>
+        <v>5.344965</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>6.759202</v>
+        <v>6.6138</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>9.692503</v>
+        <v>9.590128999999999</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.692503</v>
+        <v>9.590128999999999</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>7.963575</v>
+        <v>7.507348</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>12.436601</v>
+        <v>11.985627</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>6.373205</v>
+        <v>6.041918</v>
       </c>
     </row>
     <row r="30">
@@ -1655,25 +1655,25 @@
         <v>195.1473865248163</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>52.23217179802025</v>
+        <v>51.10635220261693</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>130.6680224752335</v>
+        <v>127.8571297390874</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>40.71376874754531</v>
+        <v>40.28374243114786</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>40.71376874754531</v>
+        <v>40.28374243114786</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>92.18780134251308</v>
+        <v>86.90643411195512</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>56.30913707429309</v>
+        <v>54.2672643163794</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>54.42172310728564</v>
+        <v>51.59281529982561</v>
       </c>
     </row>
     <row r="31">
@@ -19817,7 +19817,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -20892,7 +20892,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -21379,7 +21379,7 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">

--- a/output/pdf_financials_xlsx/UFC.xlsx
+++ b/output/pdf_financials_xlsx/UFC.xlsx
@@ -1085,7 +1085,7 @@
         <v>-0.125325</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-2.349208</v>
+        <v>-2.108</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>-1.217</v>
@@ -1237,31 +1237,31 @@
         <v>3.263182</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>3.474272</v>
+        <v>4.069163</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>7.257374</v>
+        <v>7.344757</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>4.863216</v>
+        <v>4.688709</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>6.505877</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>6.380612</v>
+        <v>6.78993</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>9.61927</v>
+        <v>9.715600999999999</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.782276</v>
+        <v>4.862132</v>
       </c>
     </row>
     <row r="21">
@@ -1357,31 +1357,31 @@
         <v>3.263182</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>3.474272</v>
+        <v>4.069163</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>7.257374</v>
+        <v>7.344757</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>4.863216</v>
+        <v>4.688709</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>6.505877</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>6.380612</v>
+        <v>6.78993</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>9.61927</v>
+        <v>9.715600999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.782276</v>
+        <v>4.862132</v>
       </c>
     </row>
     <row r="24">
@@ -1481,13 +1481,13 @@
         <v>54.386367</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>49.632457</v>
+        <v>58.1309</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>51.838386</v>
+        <v>52.46255</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>54.035733</v>
+        <v>52.096767</v>
       </c>
       <c r="G26" s="3" t="n">
         <v>54.215642</v>
@@ -1498,16 +1498,16 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>58.74636</v>
+        <v>60.676024</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>59.631888</v>
+        <v>63.45729</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>60.881456</v>
+        <v>61.491146</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>61.311231</v>
+        <v>62.335026</v>
       </c>
     </row>
     <row r="27">
@@ -1701,7 +1701,7 @@
         <v>1.854138994514441</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>24.23737191518022</v>
+        <v>21.74876809426832</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>12.5560961910458</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="E32" s="3" t="n">
-        <v>131.8020002651523</v>
+        <v>133.388972934491</v>
       </c>
       <c r="F32" s="3" t="n">
-        <v>46.50006683549881</v>
+        <v>44.83150283109054</v>
       </c>
       <c r="G32" s="3" t="n">
         <v>125.7707762036265</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>30.84582119551634</v>
+        <v>31.85902560020499</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>30.84582119551634</v>
+        <v>31.85902560020499</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>73.86313201039171</v>
+        <v>78.60147207373195</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>43.55312138619188</v>
+        <v>43.98927878028241</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>40.83654931774791</v>
+        <v>41.51845129963229</v>
       </c>
     </row>
     <row r="33">
@@ -5387,31 +5387,31 @@
         <v>3.263182</v>
       </c>
       <c r="D99" s="3" t="n">
-        <v>3.474272</v>
+        <v>4.069163</v>
       </c>
       <c r="E99" s="3" t="n">
-        <v>7.257374</v>
+        <v>7.344757</v>
       </c>
       <c r="F99" s="3" t="n">
-        <v>4.863216</v>
+        <v>4.688709</v>
       </c>
       <c r="G99" s="3" t="n">
         <v>6.505877</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="I99" s="3" t="n">
-        <v>7.343295</v>
+        <v>7.584503</v>
       </c>
       <c r="J99" s="3" t="n">
-        <v>6.380612</v>
+        <v>6.78993</v>
       </c>
       <c r="K99" s="3" t="n">
-        <v>9.61927</v>
+        <v>9.715600999999999</v>
       </c>
       <c r="L99" s="3" t="n">
-        <v>4.782276</v>
+        <v>4.862132</v>
       </c>
     </row>
     <row r="100">
@@ -6268,10 +6268,10 @@
         </is>
       </c>
       <c r="C120" s="3" t="n">
-        <v>0</v>
+        <v>-0.037553</v>
       </c>
       <c r="D120" s="3" t="n">
-        <v>0</v>
+        <v>-0.202991</v>
       </c>
       <c r="E120" s="3" t="n">
         <v>0</v>
@@ -18873,7 +18873,11 @@
           <t>Issuance of common shares, net of financing costs 21</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr"/>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
           <t>-</t>
@@ -20502,11 +20506,7 @@
           <t>Shareholders $</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -21941,11 +21941,7 @@
           <t>Shareholders ## ##### $</t>
         </is>
       </c>
-      <c r="D218" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+      <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr">
         <is>
           <t>-</t>
